--- a/chd-tt/tai-lieu/chuyen-de/BangTinh_Mau_Nhom2_SucChiuTai_MongNong.xlsx
+++ b/chd-tt/tai-lieu/chuyen-de/BangTinh_Mau_Nhom2_SucChiuTai_MongNong.xlsx
@@ -518,7 +518,7 @@
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>CHUYÊN ĐỀ BÁO CÁO NHÓM 2 — CHƯƠNG 4 (HỌC PHẦN CƠ HỌC ĐẤT GEO20202)</t>
+          <t>CHUYÊN ĐỀ BÁO CÁO NHÓM 2 — CHƯƠNG 4 (HỌC PHẦN CƠ HỌC ĐẤT GEO10404)</t>
         </is>
       </c>
     </row>
